--- a/模板/团队监控·通用.xlsx
+++ b/模板/团队监控·通用.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="1873">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5398,6 +5398,9 @@
     <t>交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n</t>
   </si>
   <si>
+    <t>^%[(.-)%]：(%d+)/(1?%d%d)\n</t>
+  </si>
+  <si>
     <t>^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。</t>
   </si>
   <si>
@@ -5441,9 +5444,6 @@
   </si>
   <si>
     <t>你的武斗值增加了30点。\n</t>
-  </si>
-  <si>
-    <t>^%[(.-)%]：(%d+)/(%d%d)\n</t>
   </si>
   <si>
     <t>^本日还能从本事件获得(%d-)贡献度的奖励。</t>
@@ -7236,7 +7236,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="62" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786116373000,</v>
+        <v>nTimeStamp = 1786166717000,</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -19634,7 +19634,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI99"/>
+  <dimension ref="A1:AI100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -19849,7 +19849,7 @@
         <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" customFormat="1" spans="1:14">
       <c r="C15" t="s">
         <v>1783</v>
       </c>
@@ -19861,16 +19861,13 @@
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" t="s">
         <v>1784</v>
       </c>
-      <c r="D16" t="s">
-        <v>1785</v>
-      </c>
       <c r="E16" t="s">
         <v>1730</v>
       </c>
@@ -19879,40 +19876,49 @@
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>634</v>
-      </c>
-      <c r="B17">
-        <v>-7</v>
+      <c r="C17" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>},[-7]={</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="C18" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+      <c r="A18" t="s">
+        <v>634</v>
+      </c>
+      <c r="B18">
+        <v>-7</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+        <v>},[-7]={</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="C19" t="s">
-        <v>1786</v>
+        <v>1766</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -19921,7 +19927,7 @@
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -19930,7 +19936,7 @@
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -19939,7 +19945,7 @@
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -19948,7 +19954,7 @@
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -19957,7 +19963,7 @@
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -19966,148 +19972,148 @@
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
+        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="C26" t="s">
-        <v>1775</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1687</v>
+        <v>1793</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="C27" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E27" t="s">
         <v>1687</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="C28" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="D28" t="s">
-        <v>1736</v>
+        <v>1774</v>
       </c>
       <c r="E28" t="s">
         <v>1687</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="C29" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="D29" t="s">
-        <v>1778</v>
+        <v>1736</v>
       </c>
       <c r="E29" t="s">
         <v>1687</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="C30" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D30" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="E30" t="s">
         <v>1687</v>
       </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="C31" t="s">
-        <v>1793</v>
+        <v>1779</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1687</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="C32" t="s">
         <v>1794</v>
       </c>
-      <c r="D32" t="s">
-        <v>1795</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="33" spans="1:35">
       <c r="C33" t="s">
-        <v>1771</v>
+        <v>1795</v>
       </c>
       <c r="D33" t="s">
-        <v>1772</v>
+        <v>1796</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="34" spans="1:35">
       <c r="C34" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="D34" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="35" spans="1:35">
       <c r="C35" t="s">
-        <v>1796</v>
+        <v>1769</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1770</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
       </c>
       <c r="N35" t="str">
         <f t="shared" ref="N35:N66" si="1">IF(ISBLANK(B35)=FALSE,IF(ISBLANK(B34),"},["&amp;B35&amp;"]={","["&amp;B35&amp;"]={"),IF(AND(ISBLANK(B35),ISBLANK(C35),ISBLANK(F35),ISBLANK(G35),OR(ISBLANK(B34)=FALSE,ISBLANK(C34)=FALSE,ISBLANK(F34)=FALSE,ISBLANK(G34)=FALSE)),"},},}",IF(ISBLANK(C35),"","{szContent="""&amp;C35&amp;""","&amp;IF(D35&lt;&gt;"","szNote="""&amp;D35&amp;""",","")&amp;IF(E35&lt;&gt;"","col={"&amp;E35&amp;"},","")&amp;IF(F35&gt;0,"bSearch=true,","")&amp;IF(G35&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H35&gt;0,"szVoice="""&amp;H35&amp;""",","")&amp;IF(I35&gt;0,"bTeamChannel=true,","")&amp;IF(J35&gt;0,"bWhisperChannel=true,","")&amp;IF(K35&gt;0,"bCenterAlarm=true,","")&amp;IF(L35&gt;0,"bScreenHead=true,","")&amp;IF(M35&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O35&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O35:AAA35)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -20116,27 +20122,21 @@
       </c>
       <c r="N36" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
+        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="37" spans="1:35">
       <c r="C37" t="s">
-        <v>1783</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
+        <v>1798</v>
       </c>
       <c r="N37" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="C38" t="s">
-        <v>1798</v>
+        <v>1784</v>
       </c>
       <c r="E38" t="s">
         <v>1730</v>
@@ -20146,12 +20146,12 @@
       </c>
       <c r="N38" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]：(%d+)/(%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="C39" t="s">
-        <v>1799</v>
+        <v>1783</v>
       </c>
       <c r="E39" t="s">
         <v>1730</v>
@@ -20161,15 +20161,12 @@
       </c>
       <c r="N39" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="40" spans="1:35">
       <c r="C40" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1785</v>
+        <v>1799</v>
       </c>
       <c r="E40" t="s">
         <v>1730</v>
@@ -20179,36 +20176,33 @@
       </c>
       <c r="N40" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="41" spans="1:35">
       <c r="C41" t="s">
-        <v>1800</v>
+        <v>1785</v>
       </c>
       <c r="D41" t="s">
-        <v>1801</v>
+        <v>1786</v>
       </c>
       <c r="E41" t="s">
-        <v>730</v>
+        <v>1730</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
       <c r="N41" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},bReg=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="42" spans="1:35">
       <c r="C42" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="D42" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="E42" t="s">
         <v>730</v>
@@ -20216,86 +20210,89 @@
       <c r="G42">
         <v>1</v>
       </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
       <c r="N42" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
+        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},bReg=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="43" spans="1:35">
-      <c r="A43" t="s">
-        <v>688</v>
-      </c>
-      <c r="B43">
-        <v>-2</v>
+      <c r="C43" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E43" t="s">
+        <v>730</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
       </c>
       <c r="N43" t="str">
         <f t="shared" si="1"/>
-        <v>},[-2]={</v>
+        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="44" spans="1:35">
-      <c r="C44" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
+      <c r="A44" t="s">
+        <v>688</v>
+      </c>
+      <c r="B44">
+        <v>-2</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>1804</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>1805</v>
-      </c>
-      <c r="AB44" t="s">
-        <v>1806</v>
-      </c>
-      <c r="AC44" t="s">
-        <v>1807</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AI44" t="s">
-        <v>1813</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="45" spans="1:35">
       <c r="C45" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G45">
+        <v>1766</v>
+      </c>
+      <c r="F45">
         <v>1</v>
       </c>
       <c r="N45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>1813</v>
       </c>
     </row>
     <row r="46" spans="1:35">
       <c r="C46" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1785</v>
+        <v>1814</v>
       </c>
       <c r="E46" t="s">
         <v>1730</v>
@@ -20305,12 +20302,15 @@
       </c>
       <c r="N46" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="47" spans="1:35">
       <c r="C47" t="s">
-        <v>1783</v>
+        <v>1785</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1786</v>
       </c>
       <c r="E47" t="s">
         <v>1730</v>
@@ -20320,360 +20320,357 @@
       </c>
       <c r="N47" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>1816</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="C48" t="s">
-        <v>1793</v>
+        <v>1784</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
       </c>
       <c r="N48" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1816</v>
       </c>
     </row>
     <row r="49" spans="3:29">
       <c r="C49" t="s">
         <v>1794</v>
       </c>
-      <c r="D49" t="s">
-        <v>1795</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
       <c r="N49" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="50" spans="3:29">
       <c r="C50" t="s">
-        <v>1817</v>
+        <v>1795</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
       </c>
       <c r="N50" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="51" spans="3:29">
       <c r="C51" t="s">
-        <v>1768</v>
+        <v>1817</v>
       </c>
       <c r="N51" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>1818</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>1819</v>
-      </c>
-      <c r="AB51" t="s">
-        <v>1820</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>1821</v>
+        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
       </c>
     </row>
     <row r="52" spans="3:29">
       <c r="C52" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="N52" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
+        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>1818</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>1820</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="53" spans="3:29">
       <c r="C53" t="s">
-        <v>1775</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1687</v>
+        <v>1767</v>
       </c>
       <c r="N53" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="54" spans="3:29">
       <c r="C54" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E54" t="s">
         <v>1687</v>
       </c>
       <c r="N54" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="55" spans="3:29">
       <c r="C55" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="D55" t="s">
-        <v>1736</v>
+        <v>1774</v>
       </c>
       <c r="E55" t="s">
         <v>1687</v>
       </c>
       <c r="N55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="56" spans="3:29">
       <c r="C56" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="D56" t="s">
-        <v>1778</v>
+        <v>1736</v>
       </c>
       <c r="E56" t="s">
         <v>1687</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:29">
       <c r="C57" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D57" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="E57" t="s">
         <v>1687</v>
       </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
       <c r="N57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:29">
       <c r="C58" t="s">
-        <v>1771</v>
+        <v>1779</v>
       </c>
       <c r="D58" t="s">
-        <v>1772</v>
+        <v>1780</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1687</v>
       </c>
       <c r="K58">
         <v>1</v>
       </c>
       <c r="N58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="59" spans="3:29">
       <c r="C59" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="D59" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="K59">
         <v>1</v>
       </c>
       <c r="N59" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="60" spans="3:29">
       <c r="C60" t="s">
-        <v>1782</v>
+        <v>1769</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1770</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
       </c>
       <c r="N60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="61" spans="3:29">
       <c r="C61" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="62" spans="3:29">
       <c r="C62" t="s">
-        <v>1822</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
+        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="63" spans="3:29">
       <c r="C63" t="s">
-        <v>1823</v>
+        <v>1822</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
       </c>
       <c r="N63" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="64" spans="3:29">
       <c r="C64" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="C65" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="N65" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="C66" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="N66" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="C67" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" ref="N67:N99" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(F67),ISBLANK(G67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(F66)=FALSE,ISBLANK(G66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(E67&lt;&gt;"","col={"&amp;E67&amp;"},","")&amp;IF(F67&gt;0,"bSearch=true,","")&amp;IF(G67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H67&gt;0,"szVoice="""&amp;H67&amp;""",","")&amp;IF(I67&gt;0,"bTeamChannel=true,","")&amp;IF(J67&gt;0,"bWhisperChannel=true,","")&amp;IF(K67&gt;0,"bCenterAlarm=true,","")&amp;IF(L67&gt;0,"bScreenHead=true,","")&amp;IF(M67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O67:AAA67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
+        <f t="shared" ref="N67:N98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(F67),ISBLANK(G67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(F66)=FALSE,ISBLANK(G66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(E67&lt;&gt;"","col={"&amp;E67&amp;"},","")&amp;IF(F67&gt;0,"bSearch=true,","")&amp;IF(G67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H67&gt;0,"szVoice="""&amp;H67&amp;""",","")&amp;IF(I67&gt;0,"bTeamChannel=true,","")&amp;IF(J67&gt;0,"bWhisperChannel=true,","")&amp;IF(K67&gt;0,"bCenterAlarm=true,","")&amp;IF(L67&gt;0,"bScreenHead=true,","")&amp;IF(M67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O67:AAA67)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="C68" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="N68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="C69" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="N69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="C70" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="N70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="C71" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="N71" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="C72" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="N72" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="C73" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="N73" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="C74" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="N74" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" t="s">
-        <v>696</v>
-      </c>
-      <c r="B75">
-        <v>-1</v>
+      <c r="C75" t="s">
+        <v>1834</v>
       </c>
       <c r="N75" t="str">
         <f t="shared" si="2"/>
-        <v>},[-1]={</v>
+        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="C76" t="s">
-        <v>1835</v>
-      </c>
-      <c r="D76" t="s">
-        <v>1836</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
+      <c r="A76" t="s">
+        <v>696</v>
+      </c>
+      <c r="B76">
+        <v>-1</v>
       </c>
       <c r="N76" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>},[-1]={</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="C77" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="D77" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -20683,315 +20680,333 @@
       </c>
       <c r="N77" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="C78" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="D78" t="s">
-        <v>1840</v>
+        <v>1838</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
       </c>
       <c r="K78">
         <v>1</v>
       </c>
       <c r="N78" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="C79" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="D79" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="K79">
         <v>1</v>
       </c>
       <c r="N79" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="C80" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="D80" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
       <c r="N80" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="81" spans="3:34">
       <c r="C81" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="D81" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="K81">
         <v>1</v>
       </c>
       <c r="N81" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="82" spans="3:34">
       <c r="C82" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F82">
+        <v>1845</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K82">
         <v>1</v>
       </c>
       <c r="N82" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>1805</v>
-      </c>
-      <c r="AA82" t="s">
-        <v>1806</v>
-      </c>
-      <c r="AB82" t="s">
-        <v>1807</v>
-      </c>
-      <c r="AC82" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AD82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AE82" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AF82" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AG82" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AH82" t="s">
-        <v>1813</v>
+        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="83" spans="3:34">
       <c r="C83" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1848</v>
-      </c>
-      <c r="K83">
+        <v>1766</v>
+      </c>
+      <c r="F83">
         <v>1</v>
       </c>
       <c r="N83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AG83" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>1813</v>
       </c>
     </row>
     <row r="84" spans="3:34">
       <c r="C84" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="D84" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="K84">
         <v>1</v>
       </c>
       <c r="N84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="85" spans="3:34">
       <c r="C85" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="D85" t="s">
-        <v>1852</v>
+        <v>1850</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
       </c>
       <c r="N85" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
+        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="86" spans="3:34">
       <c r="C86" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="D86" t="s">
-        <v>1854</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
+        <v>1852</v>
       </c>
       <c r="N86" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
       </c>
     </row>
     <row r="87" spans="3:34">
       <c r="C87" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="D87" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="N87" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="88" spans="3:34">
       <c r="C88" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="D88" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="N88" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="89" spans="3:34">
       <c r="C89" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="D89" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="K89">
         <v>1</v>
       </c>
       <c r="N89" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="90" spans="3:34">
       <c r="C90" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="D90" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="N90" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="91" spans="3:34">
       <c r="C91" t="s">
-        <v>1863</v>
+        <v>1861</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1862</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
       </c>
       <c r="N91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
+        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="92" spans="3:34">
       <c r="C92" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="N92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
+        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="93" spans="3:34">
       <c r="C93" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="N93" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
+        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="94" spans="3:34">
       <c r="C94" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="N94" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
+        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
       </c>
     </row>
     <row r="95" spans="3:34">
       <c r="C95" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1868</v>
-      </c>
-      <c r="I95">
-        <v>1</v>
+        <v>1866</v>
       </c>
       <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
+        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
       </c>
     </row>
     <row r="96" spans="3:34">
       <c r="C96" t="s">
-        <v>1869</v>
+        <v>1867</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
       </c>
       <c r="N96" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
       </c>
     </row>
     <row r="97" spans="3:14">
       <c r="C97" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="N97" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
       </c>
     </row>
     <row r="98" spans="3:14">
       <c r="C98" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D98" t="s">
-        <v>1872</v>
-      </c>
-      <c r="E98" t="s">
-        <v>718</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
+        <v>1870</v>
       </c>
       <c r="N98" t="str">
         <f t="shared" si="2"/>
+        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14">
+      <c r="C99" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E99" t="s">
+        <v>718</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="N99" t="str">
+        <f>IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(F99),ISBLANK(G99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(F98)=FALSE,ISBLANK(G98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(E99&lt;&gt;"","col={"&amp;E99&amp;"},","")&amp;IF(F99&gt;0,"bSearch=true,","")&amp;IF(G99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H99&gt;0,"szVoice="""&amp;H99&amp;""",","")&amp;IF(I99&gt;0,"bTeamChannel=true,","")&amp;IF(J99&gt;0,"bWhisperChannel=true,","")&amp;IF(K99&gt;0,"bCenterAlarm=true,","")&amp;IF(L99&gt;0,"bScreenHead=true,","")&amp;IF(M99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O99:AAA99)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
       </c>
     </row>
-    <row r="99" spans="3:14">
-      <c r="N99" t="str">
-        <f t="shared" si="2"/>
+    <row r="100" spans="3:14">
+      <c r="N100" t="str">
+        <f>IF(ISBLANK(B100)=FALSE,IF(ISBLANK(B99),"},["&amp;B100&amp;"]={","["&amp;B100&amp;"]={"),IF(AND(ISBLANK(B100),ISBLANK(C100),ISBLANK(F100),ISBLANK(G100),OR(ISBLANK(B99)=FALSE,ISBLANK(C99)=FALSE,ISBLANK(F99)=FALSE,ISBLANK(G99)=FALSE)),"},},}",IF(ISBLANK(C100),"","{szContent="""&amp;C100&amp;""","&amp;IF(D100&lt;&gt;"","szNote="""&amp;D100&amp;""",","")&amp;IF(E100&lt;&gt;"","col={"&amp;E100&amp;"},","")&amp;IF(F100&gt;0,"bSearch=true,","")&amp;IF(G100&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H100&gt;0,"szVoice="""&amp;H100&amp;""",","")&amp;IF(I100&gt;0,"bTeamChannel=true,","")&amp;IF(J100&gt;0,"bWhisperChannel=true,","")&amp;IF(K100&gt;0,"bCenterAlarm=true,","")&amp;IF(L100&gt;0,"bScreenHead=true,","")&amp;IF(M100&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O100&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O100:AAA100)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/模板/团队监控·通用.xlsx
+++ b/模板/团队监控·通用.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="1875">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5461,6 +5461,18 @@
     <t>截元丹·【{$1}】</t>
   </si>
   <si>
+    <t>财神降临！慷慨之士 {$team} 正在</t>
+  </si>
+  <si>
+    <t>【{$receiver}】·正在发红包</t>
+  </si>
+  <si>
+    <t>侠士</t>
+  </si>
+  <si>
+    <t>屏蔽·的卢·诛恶·攻防·刷马</t>
+  </si>
+  <si>
     <t>{nClass=20,nIcon=13,nFrame=5,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},</t>
   </si>
   <si>
@@ -5660,12 +5672,6 @@
   </si>
   <si>
     <t>本周已不能从本事件获得奖励。\n</t>
-  </si>
-  <si>
-    <t>财神降临！慷慨之士 {$team} 正在</t>
-  </si>
-  <si>
-    <t>【{$receiver}】·正在发红包</t>
   </si>
 </sst>
 </file>
@@ -7236,7 +7242,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="62" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786166717000,</v>
+        <v>nTimeStamp = 1786712559000,</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -19634,7 +19640,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI100"/>
+  <dimension ref="A1:AI103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -20236,568 +20242,541 @@
         <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" customFormat="1" spans="1:35">
       <c r="A44" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="B44">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
-        <v>},[-2]={</v>
-      </c>
-    </row>
-    <row r="45" spans="1:35">
+        <v>},[-3]={</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:35">
       <c r="C45" t="s">
-        <v>1766</v>
+        <v>1804</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1805</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="N45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>1804</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>1805</v>
-      </c>
-      <c r="AB45" t="s">
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",bSearch=true,[20]={},},</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:35">
+      <c r="C46" t="s">
         <v>1806</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="D46" t="s">
         <v>1807</v>
       </c>
-      <c r="AD45" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AH45" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="46" spans="1:35">
-      <c r="C46" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G46">
+      <c r="F46">
         <v>1</v>
       </c>
       <c r="N46" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="侠士",szNote="屏蔽·的卢·诛恶·攻防·刷马",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="47" spans="1:35">
-      <c r="C47" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1786</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
+      <c r="A47" t="s">
+        <v>688</v>
+      </c>
+      <c r="B47">
+        <v>-2</v>
       </c>
       <c r="N47" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="C48" t="s">
-        <v>1784</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G48">
+        <v>1766</v>
+      </c>
+      <c r="F48">
         <v>1</v>
       </c>
       <c r="N48" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
       </c>
       <c r="Z48" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AG48" t="s">
         <v>1815</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AH48" t="s">
         <v>1816</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="49" spans="3:29">
       <c r="C49" t="s">
-        <v>1794</v>
+        <v>1818</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
       </c>
       <c r="N49" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="50" spans="3:29">
       <c r="C50" t="s">
-        <v>1795</v>
+        <v>1785</v>
       </c>
       <c r="D50" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="K50">
+        <v>1786</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G50">
         <v>1</v>
       </c>
       <c r="N50" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="51" spans="3:29">
       <c r="C51" t="s">
-        <v>1817</v>
+        <v>1784</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
       </c>
       <c r="N51" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>1820</v>
       </c>
     </row>
     <row r="52" spans="3:29">
       <c r="C52" t="s">
-        <v>1768</v>
+        <v>1794</v>
       </c>
       <c r="N52" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>1818</v>
-      </c>
-      <c r="AA52" t="s">
-        <v>1819</v>
-      </c>
-      <c r="AB52" t="s">
-        <v>1820</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>1821</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="53" spans="3:29">
       <c r="C53" t="s">
-        <v>1767</v>
+        <v>1795</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
       </c>
       <c r="N53" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="54" spans="3:29">
       <c r="C54" t="s">
-        <v>1775</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1687</v>
+        <v>1821</v>
       </c>
       <c r="N54" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
       </c>
     </row>
     <row r="55" spans="3:29">
       <c r="C55" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1774</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1687</v>
+        <v>1768</v>
       </c>
       <c r="N55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>1824</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>1825</v>
       </c>
     </row>
     <row r="56" spans="3:29">
       <c r="C56" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1736</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1687</v>
+        <v>1767</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:29">
       <c r="C57" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="E57" t="s">
         <v>1687</v>
       </c>
       <c r="N57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:29">
       <c r="C58" t="s">
-        <v>1779</v>
+        <v>1773</v>
       </c>
       <c r="D58" t="s">
-        <v>1780</v>
+        <v>1774</v>
       </c>
       <c r="E58" t="s">
         <v>1687</v>
       </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
       <c r="N58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="59" spans="3:29">
       <c r="C59" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="D59" t="s">
-        <v>1772</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
+        <v>1736</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1687</v>
       </c>
       <c r="N59" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="60" spans="3:29">
       <c r="C60" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="D60" t="s">
-        <v>1770</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
+        <v>1778</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1687</v>
       </c>
       <c r="N60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="61" spans="3:29">
       <c r="C61" t="s">
-        <v>1782</v>
+        <v>1779</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1687</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="62" spans="3:29">
       <c r="C62" t="s">
-        <v>1781</v>
+        <v>1771</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1772</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="63" spans="3:29">
       <c r="C63" t="s">
-        <v>1822</v>
-      </c>
-      <c r="F63">
+        <v>1769</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1770</v>
+      </c>
+      <c r="K63">
         <v>1</v>
       </c>
       <c r="N63" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="64" spans="3:29">
       <c r="C64" t="s">
-        <v>1823</v>
+        <v>1782</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
+        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="C65" t="s">
-        <v>1824</v>
+        <v>1781</v>
       </c>
       <c r="N65" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
+        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="C66" t="s">
-        <v>1825</v>
+        <v>1826</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
       </c>
       <c r="N66" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="C67" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="N67" t="str">
         <f t="shared" ref="N67:N98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(F67),ISBLANK(G67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(F66)=FALSE,ISBLANK(G66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(E67&lt;&gt;"","col={"&amp;E67&amp;"},","")&amp;IF(F67&gt;0,"bSearch=true,","")&amp;IF(G67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H67&gt;0,"szVoice="""&amp;H67&amp;""",","")&amp;IF(I67&gt;0,"bTeamChannel=true,","")&amp;IF(J67&gt;0,"bWhisperChannel=true,","")&amp;IF(K67&gt;0,"bCenterAlarm=true,","")&amp;IF(L67&gt;0,"bScreenHead=true,","")&amp;IF(M67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O67:AAA67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="C68" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="N68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="C69" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="N69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="C70" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="N70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="C71" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="N71" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="C72" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="N72" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="C73" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="N73" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="C74" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="N74" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="C75" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="N75" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" t="s">
-        <v>696</v>
-      </c>
-      <c r="B76">
-        <v>-1</v>
+      <c r="C76" t="s">
+        <v>1836</v>
       </c>
       <c r="N76" t="str">
         <f t="shared" si="2"/>
-        <v>},[-1]={</v>
+        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="C77" t="s">
-        <v>1835</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1836</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="K77">
-        <v>1</v>
+        <v>1837</v>
       </c>
       <c r="N77" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="C78" t="s">
-        <v>1837</v>
-      </c>
-      <c r="D78" t="s">
         <v>1838</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="K78">
-        <v>1</v>
       </c>
       <c r="N78" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="C79" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1840</v>
-      </c>
-      <c r="K79">
-        <v>1</v>
+      <c r="A79" t="s">
+        <v>696</v>
+      </c>
+      <c r="B79">
+        <v>-1</v>
       </c>
       <c r="N79" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>},[-1]={</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="C80" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="D80" t="s">
-        <v>1842</v>
+        <v>1840</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
       <c r="N80" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="81" spans="3:34">
       <c r="C81" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="D81" t="s">
-        <v>1844</v>
+        <v>1842</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
       </c>
       <c r="K81">
         <v>1</v>
       </c>
       <c r="N81" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="82" spans="3:34">
       <c r="C82" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="D82" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="N82" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="83" spans="3:34">
       <c r="C83" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F83">
+        <v>1845</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K83">
         <v>1</v>
       </c>
       <c r="N83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>1805</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>1806</v>
-      </c>
-      <c r="AB83" t="s">
-        <v>1807</v>
-      </c>
-      <c r="AC83" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AD83" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AE83" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AF83" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AG83" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AH83" t="s">
-        <v>1813</v>
+        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="84" spans="3:34">
@@ -20812,7 +20791,7 @@
       </c>
       <c r="N84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="85" spans="3:34">
@@ -20827,145 +20806,181 @@
       </c>
       <c r="N85" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="86" spans="3:34">
       <c r="C86" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1852</v>
+        <v>1766</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
       </c>
       <c r="N86" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AF86" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AG86" t="s">
+        <v>1816</v>
+      </c>
+      <c r="AH86" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="87" spans="3:34">
       <c r="C87" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="D87" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="N87" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="88" spans="3:34">
       <c r="C88" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="D88" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="N88" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="89" spans="3:34">
       <c r="C89" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="D89" t="s">
-        <v>1858</v>
-      </c>
-      <c r="K89">
-        <v>1</v>
+        <v>1856</v>
       </c>
       <c r="N89" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
       </c>
     </row>
     <row r="90" spans="3:34">
       <c r="C90" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="D90" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="N90" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="91" spans="3:34">
       <c r="C91" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="D91" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="K91">
         <v>1</v>
       </c>
       <c r="N91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="92" spans="3:34">
       <c r="C92" t="s">
-        <v>1863</v>
+        <v>1861</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1862</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
       </c>
       <c r="N92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
+        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="93" spans="3:34">
       <c r="C93" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D93" t="s">
         <v>1864</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
       </c>
       <c r="N93" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
+        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="94" spans="3:34">
       <c r="C94" t="s">
         <v>1865</v>
       </c>
+      <c r="D94" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
       <c r="N94" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
+        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="95" spans="3:34">
       <c r="C95" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
+        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="96" spans="3:34">
       <c r="C96" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D96" t="s">
         <v>1868</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
       </c>
       <c r="N96" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
+        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="97" spans="3:14">
@@ -20974,7 +20989,7 @@
       </c>
       <c r="N97" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
       </c>
     </row>
     <row r="98" spans="3:14">
@@ -20983,7 +20998,7 @@
       </c>
       <c r="N98" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
       </c>
     </row>
     <row r="99" spans="3:14">
@@ -20993,20 +21008,53 @@
       <c r="D99" t="s">
         <v>1872</v>
       </c>
-      <c r="E99" t="s">
-        <v>718</v>
-      </c>
-      <c r="F99">
+      <c r="I99">
         <v>1</v>
       </c>
       <c r="N99" t="str">
         <f>IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(F99),ISBLANK(G99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(F98)=FALSE,ISBLANK(G98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(E99&lt;&gt;"","col={"&amp;E99&amp;"},","")&amp;IF(F99&gt;0,"bSearch=true,","")&amp;IF(G99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H99&gt;0,"szVoice="""&amp;H99&amp;""",","")&amp;IF(I99&gt;0,"bTeamChannel=true,","")&amp;IF(J99&gt;0,"bWhisperChannel=true,","")&amp;IF(K99&gt;0,"bCenterAlarm=true,","")&amp;IF(L99&gt;0,"bScreenHead=true,","")&amp;IF(M99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O99:AAA99)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
+        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
       </c>
     </row>
     <row r="100" spans="3:14">
+      <c r="C100" t="s">
+        <v>1873</v>
+      </c>
       <c r="N100" t="str">
         <f>IF(ISBLANK(B100)=FALSE,IF(ISBLANK(B99),"},["&amp;B100&amp;"]={","["&amp;B100&amp;"]={"),IF(AND(ISBLANK(B100),ISBLANK(C100),ISBLANK(F100),ISBLANK(G100),OR(ISBLANK(B99)=FALSE,ISBLANK(C99)=FALSE,ISBLANK(F99)=FALSE,ISBLANK(G99)=FALSE)),"},},}",IF(ISBLANK(C100),"","{szContent="""&amp;C100&amp;""","&amp;IF(D100&lt;&gt;"","szNote="""&amp;D100&amp;""",","")&amp;IF(E100&lt;&gt;"","col={"&amp;E100&amp;"},","")&amp;IF(F100&gt;0,"bSearch=true,","")&amp;IF(G100&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H100&gt;0,"szVoice="""&amp;H100&amp;""",","")&amp;IF(I100&gt;0,"bTeamChannel=true,","")&amp;IF(J100&gt;0,"bWhisperChannel=true,","")&amp;IF(K100&gt;0,"bCenterAlarm=true,","")&amp;IF(L100&gt;0,"bScreenHead=true,","")&amp;IF(M100&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O100&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O100:AAA100)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14">
+      <c r="C101" t="s">
+        <v>1874</v>
+      </c>
+      <c r="N101" t="str">
+        <f>IF(ISBLANK(B101)=FALSE,IF(ISBLANK(B100),"},["&amp;B101&amp;"]={","["&amp;B101&amp;"]={"),IF(AND(ISBLANK(B101),ISBLANK(C101),ISBLANK(F101),ISBLANK(G101),OR(ISBLANK(B100)=FALSE,ISBLANK(C100)=FALSE,ISBLANK(F100)=FALSE,ISBLANK(G100)=FALSE)),"},},}",IF(ISBLANK(C101),"","{szContent="""&amp;C101&amp;""","&amp;IF(D101&lt;&gt;"","szNote="""&amp;D101&amp;""",","")&amp;IF(E101&lt;&gt;"","col={"&amp;E101&amp;"},","")&amp;IF(F101&gt;0,"bSearch=true,","")&amp;IF(G101&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H101&gt;0,"szVoice="""&amp;H101&amp;""",","")&amp;IF(I101&gt;0,"bTeamChannel=true,","")&amp;IF(J101&gt;0,"bWhisperChannel=true,","")&amp;IF(K101&gt;0,"bCenterAlarm=true,","")&amp;IF(L101&gt;0,"bScreenHead=true,","")&amp;IF(M101&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O101&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O101:AAA101)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14">
+      <c r="C102" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E102" t="s">
+        <v>718</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="N102" t="str">
+        <f>IF(ISBLANK(B102)=FALSE,IF(ISBLANK(B101),"},["&amp;B102&amp;"]={","["&amp;B102&amp;"]={"),IF(AND(ISBLANK(B102),ISBLANK(C102),ISBLANK(F102),ISBLANK(G102),OR(ISBLANK(B101)=FALSE,ISBLANK(C101)=FALSE,ISBLANK(F101)=FALSE,ISBLANK(G101)=FALSE)),"},},}",IF(ISBLANK(C102),"","{szContent="""&amp;C102&amp;""","&amp;IF(D102&lt;&gt;"","szNote="""&amp;D102&amp;""",","")&amp;IF(E102&lt;&gt;"","col={"&amp;E102&amp;"},","")&amp;IF(F102&gt;0,"bSearch=true,","")&amp;IF(G102&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H102&gt;0,"szVoice="""&amp;H102&amp;""",","")&amp;IF(I102&gt;0,"bTeamChannel=true,","")&amp;IF(J102&gt;0,"bWhisperChannel=true,","")&amp;IF(K102&gt;0,"bCenterAlarm=true,","")&amp;IF(L102&gt;0,"bScreenHead=true,","")&amp;IF(M102&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O102&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O102:AAA102)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
+      </c>
+    </row>
+    <row r="103" spans="3:14">
+      <c r="N103" t="str">
+        <f>IF(ISBLANK(B103)=FALSE,IF(ISBLANK(B102),"},["&amp;B103&amp;"]={","["&amp;B103&amp;"]={"),IF(AND(ISBLANK(B103),ISBLANK(C103),ISBLANK(F103),ISBLANK(G103),OR(ISBLANK(B102)=FALSE,ISBLANK(C102)=FALSE,ISBLANK(F102)=FALSE,ISBLANK(G102)=FALSE)),"},},}",IF(ISBLANK(C103),"","{szContent="""&amp;C103&amp;""","&amp;IF(D103&lt;&gt;"","szNote="""&amp;D103&amp;""",","")&amp;IF(E103&lt;&gt;"","col={"&amp;E103&amp;"},","")&amp;IF(F103&gt;0,"bSearch=true,","")&amp;IF(G103&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H103&gt;0,"szVoice="""&amp;H103&amp;""",","")&amp;IF(I103&gt;0,"bTeamChannel=true,","")&amp;IF(J103&gt;0,"bWhisperChannel=true,","")&amp;IF(K103&gt;0,"bCenterAlarm=true,","")&amp;IF(L103&gt;0,"bScreenHead=true,","")&amp;IF(M103&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O103&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O103:AAA103)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/模板/团队监控·通用.xlsx
+++ b/模板/团队监控·通用.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="1875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="1875">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5347,67 +5347,67 @@
     <t>return {CHAT={</t>
   </si>
   <si>
+    <t>您已经加入战场等待队列。\n</t>
+  </si>
+  <si>
+    <t>您离开了战场的等待队列。\n</t>
+  </si>
+  <si>
+    <t>您的宠物已消除忧虑，变得活泼欢快。\n</t>
+  </si>
+  <si>
+    <t>宠物已消除忧虑</t>
+  </si>
+  <si>
+    <t>援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n</t>
+  </si>
+  <si>
+    <t>援助·已绑定</t>
+  </si>
+  <si>
+    <t>南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n</t>
+  </si>
+  <si>
+    <t>方士活动·已经开启</t>
+  </si>
+  <si>
+    <t>帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n</t>
+  </si>
+  <si>
+    <t>阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n</t>
+  </si>
+  <si>
+    <t>江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n</t>
+  </si>
+  <si>
+    <t>巴陵御兽·开启</t>
+  </si>
+  <si>
+    <t>江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n</t>
+  </si>
+  <si>
+    <t>扶摇九天·开启</t>
+  </si>
+  <si>
+    <t>交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n</t>
+  </si>
+  <si>
+    <t>交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n</t>
+  </si>
+  <si>
+    <t>^%[(.-)%]：(%d+)/(1?%d%d)\n</t>
+  </si>
+  <si>
+    <t>^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。</t>
+  </si>
+  <si>
+    <t>^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，</t>
+  </si>
+  <si>
+    <t>世界首领·出现</t>
+  </si>
+  <si>
     <t>你已进入地图</t>
-  </si>
-  <si>
-    <t>您已经加入战场等待队列。\n</t>
-  </si>
-  <si>
-    <t>您离开了战场的等待队列。\n</t>
-  </si>
-  <si>
-    <t>您的宠物已消除忧虑，变得活泼欢快。\n</t>
-  </si>
-  <si>
-    <t>宠物已消除忧虑</t>
-  </si>
-  <si>
-    <t>援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n</t>
-  </si>
-  <si>
-    <t>援助·已绑定</t>
-  </si>
-  <si>
-    <t>南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n</t>
-  </si>
-  <si>
-    <t>方士活动·已经开启</t>
-  </si>
-  <si>
-    <t>帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n</t>
-  </si>
-  <si>
-    <t>阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n</t>
-  </si>
-  <si>
-    <t>江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n</t>
-  </si>
-  <si>
-    <t>巴陵御兽·开启</t>
-  </si>
-  <si>
-    <t>江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n</t>
-  </si>
-  <si>
-    <t>扶摇九天·开启</t>
-  </si>
-  <si>
-    <t>交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n</t>
-  </si>
-  <si>
-    <t>交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n</t>
-  </si>
-  <si>
-    <t>^%[(.-)%]：(%d+)/(1?%d%d)\n</t>
-  </si>
-  <si>
-    <t>^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。</t>
-  </si>
-  <si>
-    <t>^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，</t>
-  </si>
-  <si>
-    <t>世界首领·出现</t>
   </si>
   <si>
     <t>关闭阵营模式剩余时间：5分钟。\n</t>
@@ -7242,7 +7242,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="62" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786712559000,</v>
+        <v>nTimeStamp = 1787243721000,</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -19640,7 +19640,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI103"/>
+  <dimension ref="A1:AI102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -19706,12 +19706,9 @@
       <c r="C3" t="s">
         <v>1766</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N34" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -19720,53 +19717,56 @@
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
+        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="C5" t="s">
         <v>1768</v>
       </c>
+      <c r="D5" t="s">
+        <v>1769</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="C6" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="D6" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="C7" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="D7" t="s">
-        <v>1772</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
+        <v>1773</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1687</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="C8" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D8" t="s">
         <v>1774</v>
       </c>
       <c r="E8" t="s">
@@ -19774,19 +19774,22 @@
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="C9" t="s">
         <v>1775</v>
       </c>
+      <c r="D9" t="s">
+        <v>1736</v>
+      </c>
       <c r="E9" t="s">
         <v>1687</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -19794,47 +19797,41 @@
         <v>1776</v>
       </c>
       <c r="D10" t="s">
-        <v>1736</v>
+        <v>1777</v>
       </c>
       <c r="E10" t="s">
         <v>1687</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="C11" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D11" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E11" t="s">
         <v>1687</v>
       </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="C12" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D12" t="s">
         <v>1780</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1687</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -19843,19 +19840,25 @@
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:14">
       <c r="C14" t="s">
         <v>1782</v>
       </c>
+      <c r="E14" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:14">
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="C15" t="s">
         <v>1783</v>
       </c>
@@ -19867,13 +19870,16 @@
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" t="s">
         <v>1784</v>
       </c>
+      <c r="D16" t="s">
+        <v>1785</v>
+      </c>
       <c r="E16" t="s">
         <v>1730</v>
       </c>
@@ -19882,139 +19888,136 @@
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="C17" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1786</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
+      <c r="A17" t="s">
+        <v>634</v>
+      </c>
+      <c r="B17">
+        <v>-7</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>},[-7]={</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>634</v>
-      </c>
-      <c r="B18">
-        <v>-7</v>
+      <c r="C18" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>},[-7]={</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="C19" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
+        <v>1787</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="C20" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="C21" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="C22" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="C23" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="C24" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
+        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="C25" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
+        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="C26" t="s">
-        <v>1793</v>
+        <v>1774</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1687</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="C27" t="s">
-        <v>1775</v>
+        <v>1772</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1773</v>
       </c>
       <c r="E27" t="s">
         <v>1687</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="C28" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="D28" t="s">
-        <v>1774</v>
+        <v>1736</v>
       </c>
       <c r="E28" t="s">
         <v>1687</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -20022,127 +20025,127 @@
         <v>1776</v>
       </c>
       <c r="D29" t="s">
-        <v>1736</v>
+        <v>1777</v>
       </c>
       <c r="E29" t="s">
         <v>1687</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="C30" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D30" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E30" t="s">
         <v>1687</v>
       </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="C31" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1780</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1687</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
+        <v>1794</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="C32" t="s">
-        <v>1794</v>
+        <v>1795</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="33" spans="1:35">
       <c r="C33" t="s">
-        <v>1795</v>
+        <v>1770</v>
       </c>
       <c r="D33" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
+        <v>1771</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="34" spans="1:35">
       <c r="C34" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="D34" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="35" spans="1:35">
       <c r="C35" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1770</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
+        <v>1797</v>
       </c>
       <c r="N35" t="str">
         <f t="shared" ref="N35:N66" si="1">IF(ISBLANK(B35)=FALSE,IF(ISBLANK(B34),"},["&amp;B35&amp;"]={","["&amp;B35&amp;"]={"),IF(AND(ISBLANK(B35),ISBLANK(C35),ISBLANK(F35),ISBLANK(G35),OR(ISBLANK(B34)=FALSE,ISBLANK(C34)=FALSE,ISBLANK(F34)=FALSE,ISBLANK(G34)=FALSE)),"},},}",IF(ISBLANK(C35),"","{szContent="""&amp;C35&amp;""","&amp;IF(D35&lt;&gt;"","szNote="""&amp;D35&amp;""",","")&amp;IF(E35&lt;&gt;"","col={"&amp;E35&amp;"},","")&amp;IF(F35&gt;0,"bSearch=true,","")&amp;IF(G35&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H35&gt;0,"szVoice="""&amp;H35&amp;""",","")&amp;IF(I35&gt;0,"bTeamChannel=true,","")&amp;IF(J35&gt;0,"bWhisperChannel=true,","")&amp;IF(K35&gt;0,"bCenterAlarm=true,","")&amp;IF(L35&gt;0,"bScreenHead=true,","")&amp;IF(M35&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O35&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O35:AAA35)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="36" spans="1:35">
       <c r="C36" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="N36" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
+        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="37" spans="1:35">
       <c r="C37" t="s">
-        <v>1798</v>
+        <v>1783</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
       </c>
       <c r="N37" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="C38" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="E38" t="s">
         <v>1730</v>
@@ -20152,12 +20155,12 @@
       </c>
       <c r="N38" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="C39" t="s">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="E39" t="s">
         <v>1730</v>
@@ -20167,12 +20170,15 @@
       </c>
       <c r="N39" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="40" spans="1:35">
       <c r="C40" t="s">
-        <v>1799</v>
+        <v>1784</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1785</v>
       </c>
       <c r="E40" t="s">
         <v>1730</v>
@@ -20182,33 +20188,36 @@
       </c>
       <c r="N40" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="41" spans="1:35">
       <c r="C41" t="s">
-        <v>1785</v>
+        <v>1800</v>
       </c>
       <c r="D41" t="s">
-        <v>1786</v>
+        <v>1801</v>
       </c>
       <c r="E41" t="s">
-        <v>1730</v>
+        <v>730</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
       <c r="N41" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},bReg=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="42" spans="1:35">
       <c r="C42" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="D42" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="E42" t="s">
         <v>730</v>
@@ -20216,131 +20225,128 @@
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
       <c r="N42" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},bReg=true,[20]={bCenterAlarm=true,},},</v>
-      </c>
-    </row>
-    <row r="43" spans="1:35">
-      <c r="C43" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1803</v>
-      </c>
-      <c r="E43" t="s">
-        <v>730</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
+        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:35">
+      <c r="A43" t="s">
+        <v>677</v>
+      </c>
+      <c r="B43">
+        <v>-3</v>
       </c>
       <c r="N43" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
+        <v>},[-3]={</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:35">
-      <c r="A44" t="s">
-        <v>677</v>
-      </c>
-      <c r="B44">
-        <v>-3</v>
+      <c r="C44" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
-        <v>},[-3]={</v>
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:35">
       <c r="C45" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D45" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="N45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",bSearch=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:35">
-      <c r="C46" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1807</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
+        <v>{szContent="侠士",szNote="屏蔽·的卢·诛恶·攻防·刷马",bSearch=true,[20]={},},</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35">
+      <c r="A46" t="s">
+        <v>688</v>
+      </c>
+      <c r="B46">
+        <v>-2</v>
       </c>
       <c r="N46" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="侠士",szNote="屏蔽·的卢·诛恶·攻防·刷马",bSearch=true,[20]={},},</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="47" spans="1:35">
-      <c r="A47" t="s">
-        <v>688</v>
-      </c>
-      <c r="B47">
-        <v>-2</v>
+      <c r="C47" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
       </c>
       <c r="N47" t="str">
         <f t="shared" si="1"/>
-        <v>},[-2]={</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>1816</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="C48" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F48">
+        <v>1818</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
       <c r="N48" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AB48" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>1813</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>1814</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AH48" t="s">
-        <v>1816</v>
-      </c>
-      <c r="AI48" t="s">
-        <v>1817</v>
+        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="49" spans="3:29">
       <c r="C49" t="s">
-        <v>1818</v>
+        <v>1784</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1785</v>
       </c>
       <c r="E49" t="s">
         <v>1730</v>
@@ -20350,15 +20356,12 @@
       </c>
       <c r="N49" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
       </c>
     </row>
     <row r="50" spans="3:29">
       <c r="C50" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="E50" t="s">
         <v>1730</v>
@@ -20368,121 +20371,121 @@
       </c>
       <c r="N50" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>1820</v>
       </c>
     </row>
     <row r="51" spans="3:29">
       <c r="C51" t="s">
-        <v>1784</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
+        <v>1794</v>
       </c>
       <c r="N51" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>1819</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>1820</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="52" spans="3:29">
       <c r="C52" t="s">
-        <v>1794</v>
+        <v>1795</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
       </c>
       <c r="N52" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="53" spans="3:29">
       <c r="C53" t="s">
-        <v>1795</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
+        <v>1821</v>
       </c>
       <c r="N53" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
       </c>
     </row>
     <row r="54" spans="3:29">
       <c r="C54" t="s">
-        <v>1821</v>
+        <v>1767</v>
       </c>
       <c r="N54" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
+        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>1824</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>1825</v>
       </c>
     </row>
     <row r="55" spans="3:29">
       <c r="C55" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="N55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>1822</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>1823</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>1824</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>1825</v>
+        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="56" spans="3:29">
       <c r="C56" t="s">
-        <v>1767</v>
+        <v>1774</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1687</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:29">
       <c r="C57" t="s">
-        <v>1775</v>
+        <v>1772</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1773</v>
       </c>
       <c r="E57" t="s">
         <v>1687</v>
       </c>
       <c r="N57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:29">
       <c r="C58" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="D58" t="s">
-        <v>1774</v>
+        <v>1736</v>
       </c>
       <c r="E58" t="s">
         <v>1687</v>
       </c>
       <c r="N58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="59" spans="3:29">
@@ -20490,235 +20493,238 @@
         <v>1776</v>
       </c>
       <c r="D59" t="s">
-        <v>1736</v>
+        <v>1777</v>
       </c>
       <c r="E59" t="s">
         <v>1687</v>
       </c>
       <c r="N59" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="60" spans="3:29">
       <c r="C60" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D60" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E60" t="s">
         <v>1687</v>
       </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
       <c r="N60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="61" spans="3:29">
       <c r="C61" t="s">
-        <v>1779</v>
+        <v>1770</v>
       </c>
       <c r="D61" t="s">
-        <v>1780</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1687</v>
+        <v>1771</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="62" spans="3:29">
       <c r="C62" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="D62" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="63" spans="3:29">
       <c r="C63" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1770</v>
-      </c>
-      <c r="K63">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="N63" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="64" spans="3:29">
       <c r="C64" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="C65" t="s">
-        <v>1781</v>
+        <v>1826</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
       </c>
       <c r="N65" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="C66" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F66">
-        <v>1</v>
+        <v>1827</v>
       </c>
       <c r="N66" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
+        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="C67" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="N67" t="str">
         <f t="shared" ref="N67:N98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(F67),ISBLANK(G67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(F66)=FALSE,ISBLANK(G66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(E67&lt;&gt;"","col={"&amp;E67&amp;"},","")&amp;IF(F67&gt;0,"bSearch=true,","")&amp;IF(G67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H67&gt;0,"szVoice="""&amp;H67&amp;""",","")&amp;IF(I67&gt;0,"bTeamChannel=true,","")&amp;IF(J67&gt;0,"bWhisperChannel=true,","")&amp;IF(K67&gt;0,"bCenterAlarm=true,","")&amp;IF(L67&gt;0,"bScreenHead=true,","")&amp;IF(M67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O67:AAA67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="C68" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="N68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="C69" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="N69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="C70" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="N70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="C71" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="N71" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="C72" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="N72" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="C73" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="N73" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="C74" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="N74" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="C75" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="N75" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="C76" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="N76" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="C77" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="N77" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="78" spans="1:14">
-      <c r="C78" t="s">
-        <v>1838</v>
+      <c r="A78" t="s">
+        <v>696</v>
+      </c>
+      <c r="B78">
+        <v>-1</v>
       </c>
       <c r="N78" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
+        <v>},[-1]={</v>
       </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" t="s">
-        <v>696</v>
-      </c>
-      <c r="B79">
-        <v>-1</v>
+      <c r="C79" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
       </c>
       <c r="N79" t="str">
         <f t="shared" si="2"/>
-        <v>},[-1]={</v>
+        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="C80" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="D80" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -20728,333 +20734,315 @@
       </c>
       <c r="N80" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="81" spans="3:34">
       <c r="C81" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="D81" t="s">
-        <v>1842</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
+        <v>1844</v>
       </c>
       <c r="K81">
         <v>1</v>
       </c>
       <c r="N81" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="82" spans="3:34">
       <c r="C82" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="D82" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="N82" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="83" spans="3:34">
       <c r="C83" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="D83" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="K83">
         <v>1</v>
       </c>
       <c r="N83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="84" spans="3:34">
       <c r="C84" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="D84" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="K84">
         <v>1</v>
       </c>
       <c r="N84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="85" spans="3:34">
       <c r="C85" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1850</v>
-      </c>
-      <c r="K85">
+        <v>1786</v>
+      </c>
+      <c r="F85">
         <v>1</v>
       </c>
       <c r="N85" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AF85" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AG85" t="s">
+        <v>1816</v>
+      </c>
+      <c r="AH85" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="86" spans="3:34">
       <c r="C86" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F86">
+        <v>1851</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1852</v>
+      </c>
+      <c r="K86">
         <v>1</v>
       </c>
       <c r="N86" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AA86" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AB86" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AC86" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AD86" t="s">
-        <v>1813</v>
-      </c>
-      <c r="AE86" t="s">
-        <v>1814</v>
-      </c>
-      <c r="AF86" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AG86" t="s">
-        <v>1816</v>
-      </c>
-      <c r="AH86" t="s">
-        <v>1817</v>
+        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="87" spans="3:34">
       <c r="C87" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="D87" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="N87" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="88" spans="3:34">
       <c r="C88" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="D88" t="s">
-        <v>1854</v>
-      </c>
-      <c r="K88">
-        <v>1</v>
+        <v>1856</v>
       </c>
       <c r="N88" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
       </c>
     </row>
     <row r="89" spans="3:34">
       <c r="C89" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="D89" t="s">
-        <v>1856</v>
+        <v>1858</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
       </c>
       <c r="N89" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
+        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="90" spans="3:34">
       <c r="C90" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="D90" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="N90" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="91" spans="3:34">
       <c r="C91" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D91" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="K91">
         <v>1</v>
       </c>
       <c r="N91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="92" spans="3:34">
       <c r="C92" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="D92" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="K92">
         <v>1</v>
       </c>
       <c r="N92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="93" spans="3:34">
       <c r="C93" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="D93" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="N93" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="94" spans="3:34">
       <c r="C94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1866</v>
-      </c>
-      <c r="K94">
-        <v>1</v>
+        <v>1867</v>
       </c>
       <c r="N94" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="95" spans="3:34">
       <c r="C95" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
+        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="96" spans="3:34">
       <c r="C96" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="N96" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
+        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
       </c>
     </row>
     <row r="97" spans="3:14">
       <c r="C97" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="N97" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
+        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
       </c>
     </row>
     <row r="98" spans="3:14">
       <c r="C98" t="s">
-        <v>1870</v>
+        <v>1871</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1872</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
       </c>
       <c r="N98" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
+        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
       </c>
     </row>
     <row r="99" spans="3:14">
       <c r="C99" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D99" t="s">
-        <v>1872</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
+        <v>1873</v>
       </c>
       <c r="N99" t="str">
         <f>IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(F99),ISBLANK(G99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(F98)=FALSE,ISBLANK(G98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(E99&lt;&gt;"","col={"&amp;E99&amp;"},","")&amp;IF(F99&gt;0,"bSearch=true,","")&amp;IF(G99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H99&gt;0,"szVoice="""&amp;H99&amp;""",","")&amp;IF(I99&gt;0,"bTeamChannel=true,","")&amp;IF(J99&gt;0,"bWhisperChannel=true,","")&amp;IF(K99&gt;0,"bCenterAlarm=true,","")&amp;IF(L99&gt;0,"bScreenHead=true,","")&amp;IF(M99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O99:AAA99)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
+        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
       </c>
     </row>
     <row r="100" spans="3:14">
       <c r="C100" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="N100" t="str">
         <f>IF(ISBLANK(B100)=FALSE,IF(ISBLANK(B99),"},["&amp;B100&amp;"]={","["&amp;B100&amp;"]={"),IF(AND(ISBLANK(B100),ISBLANK(C100),ISBLANK(F100),ISBLANK(G100),OR(ISBLANK(B99)=FALSE,ISBLANK(C99)=FALSE,ISBLANK(F99)=FALSE,ISBLANK(G99)=FALSE)),"},},}",IF(ISBLANK(C100),"","{szContent="""&amp;C100&amp;""","&amp;IF(D100&lt;&gt;"","szNote="""&amp;D100&amp;""",","")&amp;IF(E100&lt;&gt;"","col={"&amp;E100&amp;"},","")&amp;IF(F100&gt;0,"bSearch=true,","")&amp;IF(G100&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H100&gt;0,"szVoice="""&amp;H100&amp;""",","")&amp;IF(I100&gt;0,"bTeamChannel=true,","")&amp;IF(J100&gt;0,"bWhisperChannel=true,","")&amp;IF(K100&gt;0,"bCenterAlarm=true,","")&amp;IF(L100&gt;0,"bScreenHead=true,","")&amp;IF(M100&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O100&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O100:AAA100)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
       </c>
     </row>
     <row r="101" spans="3:14">
       <c r="C101" t="s">
-        <v>1874</v>
+        <v>1804</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E101" t="s">
+        <v>718</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
       </c>
       <c r="N101" t="str">
         <f>IF(ISBLANK(B101)=FALSE,IF(ISBLANK(B100),"},["&amp;B101&amp;"]={","["&amp;B101&amp;"]={"),IF(AND(ISBLANK(B101),ISBLANK(C101),ISBLANK(F101),ISBLANK(G101),OR(ISBLANK(B100)=FALSE,ISBLANK(C100)=FALSE,ISBLANK(F100)=FALSE,ISBLANK(G100)=FALSE)),"},},}",IF(ISBLANK(C101),"","{szContent="""&amp;C101&amp;""","&amp;IF(D101&lt;&gt;"","szNote="""&amp;D101&amp;""",","")&amp;IF(E101&lt;&gt;"","col={"&amp;E101&amp;"},","")&amp;IF(F101&gt;0,"bSearch=true,","")&amp;IF(G101&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H101&gt;0,"szVoice="""&amp;H101&amp;""",","")&amp;IF(I101&gt;0,"bTeamChannel=true,","")&amp;IF(J101&gt;0,"bWhisperChannel=true,","")&amp;IF(K101&gt;0,"bCenterAlarm=true,","")&amp;IF(L101&gt;0,"bScreenHead=true,","")&amp;IF(M101&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O101&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O101:AAA101)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
       </c>
     </row>
     <row r="102" spans="3:14">
-      <c r="C102" t="s">
-        <v>1804</v>
-      </c>
-      <c r="D102" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E102" t="s">
-        <v>718</v>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
       <c r="N102" t="str">
         <f>IF(ISBLANK(B102)=FALSE,IF(ISBLANK(B101),"},["&amp;B102&amp;"]={","["&amp;B102&amp;"]={"),IF(AND(ISBLANK(B102),ISBLANK(C102),ISBLANK(F102),ISBLANK(G102),OR(ISBLANK(B101)=FALSE,ISBLANK(C101)=FALSE,ISBLANK(F101)=FALSE,ISBLANK(G101)=FALSE)),"},},}",IF(ISBLANK(C102),"","{szContent="""&amp;C102&amp;""","&amp;IF(D102&lt;&gt;"","szNote="""&amp;D102&amp;""",","")&amp;IF(E102&lt;&gt;"","col={"&amp;E102&amp;"},","")&amp;IF(F102&gt;0,"bSearch=true,","")&amp;IF(G102&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H102&gt;0,"szVoice="""&amp;H102&amp;""",","")&amp;IF(I102&gt;0,"bTeamChannel=true,","")&amp;IF(J102&gt;0,"bWhisperChannel=true,","")&amp;IF(K102&gt;0,"bCenterAlarm=true,","")&amp;IF(L102&gt;0,"bScreenHead=true,","")&amp;IF(M102&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O102&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O102:AAA102)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="103" spans="3:14">
-      <c r="N103" t="str">
-        <f>IF(ISBLANK(B103)=FALSE,IF(ISBLANK(B102),"},["&amp;B103&amp;"]={","["&amp;B103&amp;"]={"),IF(AND(ISBLANK(B103),ISBLANK(C103),ISBLANK(F103),ISBLANK(G103),OR(ISBLANK(B102)=FALSE,ISBLANK(C102)=FALSE,ISBLANK(F102)=FALSE,ISBLANK(G102)=FALSE)),"},},}",IF(ISBLANK(C103),"","{szContent="""&amp;C103&amp;""","&amp;IF(D103&lt;&gt;"","szNote="""&amp;D103&amp;""",","")&amp;IF(E103&lt;&gt;"","col={"&amp;E103&amp;"},","")&amp;IF(F103&gt;0,"bSearch=true,","")&amp;IF(G103&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H103&gt;0,"szVoice="""&amp;H103&amp;""",","")&amp;IF(I103&gt;0,"bTeamChannel=true,","")&amp;IF(J103&gt;0,"bWhisperChannel=true,","")&amp;IF(K103&gt;0,"bCenterAlarm=true,","")&amp;IF(L103&gt;0,"bScreenHead=true,","")&amp;IF(M103&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O103&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O103:AAA103)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/模板/团队监控·通用.xlsx
+++ b/模板/团队监控·通用.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="1875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="1873">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5389,19 +5389,13 @@
     <t>扶摇九天·开启</t>
   </si>
   <si>
-    <t>交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n</t>
-  </si>
-  <si>
-    <t>交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n</t>
-  </si>
-  <si>
     <t>^%[(.-)%]：(%d+)/(1?%d%d)\n</t>
   </si>
   <si>
     <t>^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。</t>
   </si>
   <si>
-    <t>^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，</t>
+    <t>^密探来报：\"(.-)\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，</t>
   </si>
   <si>
     <t>世界首领·出现</t>
@@ -7242,7 +7236,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="62" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1787243721000,</v>
+        <v>nTimeStamp = 1787331150000,</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -18699,12 +18693,9 @@
       <c r="E5" t="s">
         <v>1684</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
       <c r="O5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",bReg=true,[14]={},},</v>
+        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",[14]={},},</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -18720,15 +18711,9 @@
       <c r="F6" t="s">
         <v>1687</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
       <c r="O6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},bReg=true,[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -18783,12 +18768,9 @@
       <c r="E10" t="s">
         <v>1693</v>
       </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
       <c r="O10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="转换失败，可能是道具即将超过拥有上限。",szTarget="%",szNote="宝箱·转换失败·可能上限",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="转换失败，可能是道具即将超过拥有上限。",szTarget="%",szNote="宝箱·转换失败·可能上限",[14]={},},</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -18801,12 +18783,9 @@
       <c r="E11" t="s">
         <v>1695</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
       <c r="O11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="(.-)([增加扣除]-)(%d+)个【(.-)】。",szTarget="%",szNote="{$2}【{$2}】{$1}个",bReg=true,[14]={},},</v>
+        <v>{szContent="(.-)([增加扣除]-)(%d+)个【(.-)】。",szTarget="%",szNote="{$2}【{$2}】{$1}个",[14]={},},</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -18819,12 +18798,9 @@
       <c r="E12" t="s">
         <v>1684</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
       <c r="O12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",bReg=true,[14]={},},</v>
+        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",[14]={},},</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -18834,12 +18810,9 @@
       <c r="D13" t="s">
         <v>1696</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
       <c r="O13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^本周已获得送花奖励次数 (%d-)/(%d+)",szTarget="%",bReg=true,[14]={},},</v>
+        <v>{szContent="^本周已获得送花奖励次数 (%d-)/(%d+)",szTarget="%",[14]={},},</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -18849,12 +18822,9 @@
       <c r="D14" t="s">
         <v>1697</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
       <c r="O14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^本周还可通过配置香膏获得调香经验(%d+)次",szTarget="%",bReg=true,[14]={},},</v>
+        <v>{szContent="^本周还可通过配置香膏获得调香经验(%d+)次",szTarget="%",[14]={},},</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -18867,12 +18837,9 @@
       <c r="E15" t="s">
         <v>1699</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
       <c r="O15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^大侠已经触发过%[(.-)%]奇遇，或者拥有该奇遇的概率提升状态，故奖励(%d-)点不占周上限的园宅币。",szTarget="%",szNote="祈福树·[{$1}]转{$2}园宅币",bReg=true,[14]={},},</v>
+        <v>{szContent="^大侠已经触发过%[(.-)%]奇遇，或者拥有该奇遇的概率提升状态，故奖励(%d-)点不占周上限的园宅币。",szTarget="%",szNote="祈福树·[{$1}]转{$2}园宅币",[14]={},},</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -18885,15 +18852,9 @@
       <c r="E16" t="s">
         <v>1701</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^恭喜侠士获得“(.-)”增益！",szTarget="%",szNote="祈福树·增益·{$1}",bReg=true,[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="^恭喜侠士获得“(.-)”增益！",szTarget="%",szNote="祈福树·增益·{$1}",[14]={},},</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -18957,12 +18918,9 @@
       <c r="E23" t="s">
         <v>1708</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
       <c r="O23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="成功重置原野奇踪进度",szNote="成功重置原野奇踪进度",[14]={bTeamChannel=true,},},</v>
+        <v>{szContent="成功重置原野奇踪进度",szNote="成功重置原野奇踪进度",[14]={},},</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -18981,15 +18939,9 @@
       <c r="E25" t="s">
         <v>1711</v>
       </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
       <c r="O25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^请将这单货物送往(.-)号宅邸的管家阿甘处。",szNote="送信·{$1}",bReg=true,[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="^请将这单货物送往(.-)号宅邸的管家阿甘处。",szNote="送信·{$1}",[14]={},},</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -19017,12 +18969,9 @@
       <c r="F27" t="s">
         <v>1687</v>
       </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
       <c r="O27" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="运货首领被击杀，损失了10份镖银……",szTarget="%",szNote="阴山商路·首领重伤·损失10镖银",col={100,255,255,},[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="运货首领被击杀，损失了10份镖银……",szTarget="%",szNote="阴山商路·首领重伤·损失10镖银",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -19038,12 +18987,9 @@
       <c r="F28" t="s">
         <v>1687</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
       <c r="O28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="运货首领离线了，损失了20份镖银……",szTarget="%",szNote="阴山商路·首领离线·损失20镖银",col={100,255,255,},[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="运货首领离线了，损失了20份镖银……",szTarget="%",szNote="阴山商路·首领离线·损失20镖银",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -19059,12 +19005,9 @@
       <c r="F29" t="s">
         <v>1687</v>
       </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
       <c r="O29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="运货首领花费5000两帮会资金成功补货50份！",szTarget="%",szNote="阴山商路·补货·50份",col={100,255,255,},[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="运货首领花费5000两帮会资金成功补货50份！",szTarget="%",szNote="阴山商路·补货·50份",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -19080,12 +19023,9 @@
       <c r="F30" t="s">
         <v>1687</v>
       </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
       <c r="O30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="运货首领身份已重置，请各位尽快认领物资队将其运抵目的地！",szTarget="%",szNote="阴山商路·首领重置·损失30镖银",col={100,255,255,},[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="运货首领身份已重置，请各位尽快认领物资队将其运抵目的地！",szTarget="%",szNote="阴山商路·首领重置·损失30镖银",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -19101,15 +19041,9 @@
       <c r="F31" t="s">
         <v>1687</v>
       </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
       <c r="O31" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},bReg=true,[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -19164,12 +19098,9 @@
       <c r="E36" t="s">
         <v>1722</v>
       </c>
-      <c r="L36">
-        <v>1</v>
-      </c>
       <c r="O36" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="祈愿未触发，当前已尝试次数为： 1",szTarget="%",szNote="祈愿台·尝试·1次",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="祈愿未触发，当前已尝试次数为： 1",szTarget="%",szNote="祈愿台·尝试·1次",[14]={},},</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -19182,12 +19113,9 @@
       <c r="E37" t="s">
         <v>1724</v>
       </c>
-      <c r="L37">
-        <v>1</v>
-      </c>
       <c r="O37" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="祈愿未触发，当前已尝试次数为： 2",szTarget="%",szNote="祈愿台·尝试·2次",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="祈愿未触发，当前已尝试次数为： 2",szTarget="%",szNote="祈愿台·尝试·2次",[14]={},},</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -19200,12 +19128,9 @@
       <c r="E38" t="s">
         <v>1726</v>
       </c>
-      <c r="L38">
-        <v>1</v>
-      </c>
       <c r="O38" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="宝光闪闪，祈愿触发！",szTarget="%",szNote="祈愿台·祈愿触发",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="宝光闪闪，祈愿触发！",szTarget="%",szNote="祈愿台·祈愿触发",[14]={},},</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -19230,12 +19155,9 @@
       <c r="E40" t="s">
         <v>1684</v>
       </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
       <c r="O40" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",bReg=true,[14]={},},</v>
+        <v>{szContent="^大侠的(.-)运势累计至(%d-)/(%d+)",szTarget="%",szNote="运势·{$1}·{$2}/{$3}",[14]={},},</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -19251,15 +19173,9 @@
       <c r="F41" t="s">
         <v>1687</v>
       </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
-      </c>
       <c r="O41" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},bReg=true,[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="(.-)已经登记成为送货首领，物资队已出发，请帮会成员立即集合护送！",szTarget="%",szNote="阴山商路·【{$1}】·送货首领",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -19269,12 +19185,9 @@
       <c r="D42" t="s">
         <v>1727</v>
       </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
       <c r="O42" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="{$me}这是什么乱七八糟的水沏的，白白浪费了上好的",szTarget="%",bSearch=true,[14]={},},</v>
+        <v>{szContent="{$me}这是什么乱七八糟的水沏的，白白浪费了上好的",szTarget="%",[14]={},},</v>
       </c>
     </row>
     <row r="43" spans="1:15">
@@ -19305,12 +19218,9 @@
       <c r="F45" t="s">
         <v>1730</v>
       </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
       <c r="O45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="因(.-)交通阻塞，镖局临时开启【(.-)】秘境镖路，各位侠士可寻我直接进入秘境。",szTarget="秘境镖局接引人",col={255,255,100,},bReg=true,[14]={},},</v>
+        <v>{szContent="因(.-)交通阻塞，镖局临时开启【(.-)】秘境镖路，各位侠士可寻我直接进入秘境。",szTarget="秘境镖局接引人",col={255,255,100,},[14]={},},</v>
       </c>
     </row>
     <row r="46" spans="1:15">
@@ -19335,12 +19245,9 @@
       <c r="E47" t="s">
         <v>1732</v>
       </c>
-      <c r="L47">
-        <v>1</v>
-      </c>
       <c r="O47" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="好像有鱼咬钩了，快收杆！",szTarget="%",szNote="有鱼咬钩",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="好像有鱼咬钩了，快收杆！",szTarget="%",szNote="有鱼咬钩",[14]={},},</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -19356,12 +19263,10 @@
       <c r="F48" t="s">
         <v>1687</v>
       </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
+      <c r="G48"/>
       <c r="O48" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="此次帮会通过阴山商路成功运抵",szTarget="%",szNote="阴山商路·成功运抵",col={100,255,255,},bSearch=true,[14]={},},</v>
+        <v>{szContent="此次帮会通过阴山商路成功运抵",szTarget="%",szNote="阴山商路·成功运抵",col={100,255,255,},[14]={},},</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -19467,12 +19372,9 @@
       <c r="E55" t="s">
         <v>1748</v>
       </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
       <c r="O55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你在挖掘宝藏时消耗了",szTarget="%",szNote="挖宝·CD",bSearch=true,[14]={},},</v>
+        <v>{szContent="你在挖掘宝藏时消耗了",szTarget="%",szNote="挖宝·CD",[14]={},},</v>
       </c>
     </row>
     <row r="56" spans="3:15">
@@ -19485,12 +19387,9 @@
       <c r="F56" t="s">
         <v>1730</v>
       </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
       <c r="O56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你已累计翻阅了(%d-)次《(.-)传》。",szTarget="%",col={255,255,100,},bReg=true,[14]={},},</v>
+        <v>{szContent="^你已累计翻阅了(%d-)次《(.-)传》。",szTarget="%",col={255,255,100,},[14]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:15">
@@ -19506,12 +19405,9 @@
       <c r="F57" t="s">
         <v>1730</v>
       </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
       <c r="O57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你不能在%[(.-)%]附近(%d-)尺内执行此操作。",szTarget="%",szNote="注意·[{$1}]·限制{$2}尺",col={255,255,100,},bReg=true,[14]={},},</v>
+        <v>{szContent="^你不能在%[(.-)%]附近(%d-)尺内执行此操作。",szTarget="%",szNote="注意·[{$1}]·限制{$2}尺",col={255,255,100,},[14]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:15">
@@ -19524,12 +19420,9 @@
       <c r="E58" t="s">
         <v>1753</v>
       </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
       <c r="O58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="少侠奇穴重置，特补偿九花玉露散200个已通过邮件发送，请注意查收。",szTarget="%",szNote="奇穴重置",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="少侠奇穴重置，特补偿九花玉露散200个已通过邮件发送，请注意查收。",szTarget="%",szNote="奇穴重置",[14]={},},</v>
       </c>
     </row>
     <row r="59" spans="3:15">
@@ -19548,12 +19441,9 @@
       <c r="E60" t="s">
         <v>1756</v>
       </c>
-      <c r="L60">
-        <v>1</v>
-      </c>
       <c r="O60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你发现了一个藏宝洞！藏宝洞只存在两刻钟，务必速速前往挖掘宝藏！",szNote="发现·藏宝洞",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你发现了一个藏宝洞！藏宝洞只存在两刻钟，务必速速前往挖掘宝藏！",szNote="发现·藏宝洞",[14]={},},</v>
       </c>
     </row>
     <row r="61" spans="3:15">
@@ -19563,12 +19453,9 @@
       <c r="E61" t="s">
         <v>1758</v>
       </c>
-      <c r="L61">
-        <v>1</v>
-      </c>
       <c r="O61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="团队宝藏点出现！只存在一刻钟，速去寻找！",szNote="团点出现",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="团队宝藏点出现！只存在一刻钟，速去寻找！",szNote="团点出现",[14]={},},</v>
       </c>
     </row>
     <row r="62" spans="3:15">
@@ -19578,12 +19465,9 @@
       <c r="E62" t="s">
         <v>1760</v>
       </c>
-      <c r="L62">
-        <v>1</v>
-      </c>
       <c r="O62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你在探寻魂墟宝物时不小心惊动了魂墟看守宝物的魂灵！",szNote="方士寻宝·魂灵宝物",[14]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你在探寻魂墟宝物时不小心惊动了魂墟看守宝物的魂灵！",szNote="方士寻宝·魂灵宝物",[14]={},},</v>
       </c>
     </row>
     <row r="63" spans="3:15">
@@ -19611,15 +19495,9 @@
       <c r="F64" t="s">
         <v>718</v>
       </c>
-      <c r="L64">
-        <v>1</v>
-      </c>
-      <c r="N64">
-        <v>1</v>
-      </c>
       <c r="O64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="注意，你已被发布决斗挑战，决斗挑战正式生效！",szNote="决斗挑战·正式生效",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},},</v>
+        <v>{szContent="注意，你已被发布决斗挑战，决斗挑战正式生效！",szNote="决斗挑战·正式生效",col={255,50,255,},[14]={},},</v>
       </c>
     </row>
     <row r="65" spans="15:15">
@@ -19640,7 +19518,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI102"/>
+  <dimension ref="A1:AI98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -19727,12 +19605,9 @@
       <c r="D5" t="s">
         <v>1769</v>
       </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={},},</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -19742,12 +19617,9 @@
       <c r="D6" t="s">
         <v>1771</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={},},</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -19817,1232 +19689,1056 @@
       <c r="E11" t="s">
         <v>1687</v>
       </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:14">
       <c r="C12" t="s">
         <v>1780</v>
       </c>
+      <c r="E12" t="s">
+        <v>1730</v>
+      </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="C13" t="s">
         <v>1781</v>
       </c>
+      <c r="E13" t="s">
+        <v>1730</v>
+      </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:14">
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="C14" t="s">
         <v>1782</v>
       </c>
+      <c r="D14" t="s">
+        <v>1783</v>
+      </c>
       <c r="E14" t="s">
         <v>1730</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^密探来报：\"(.-)\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="C15" t="s">
-        <v>1783</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
+      <c r="A15" t="s">
+        <v>634</v>
+      </c>
+      <c r="B15">
+        <v>-7</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>},[-7]={</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" t="s">
         <v>1784</v>
       </c>
-      <c r="D16" t="s">
-        <v>1785</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>634</v>
-      </c>
-      <c r="B17">
-        <v>-7</v>
+        <v>{szContent="你已进入地图",[20]={},},</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14">
+      <c r="C17" t="s">
+        <v>1785</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>},[-7]={</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14">
       <c r="C18" t="s">
         <v>1786</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14">
       <c r="C19" t="s">
         <v>1787</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：5分钟。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14">
       <c r="C20" t="s">
         <v>1788</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：4分钟。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14">
       <c r="C21" t="s">
         <v>1789</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：3分钟。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14">
       <c r="C22" t="s">
         <v>1790</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：2分钟。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14">
       <c r="C23" t="s">
         <v>1791</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式剩余时间：1分钟。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14">
       <c r="C24" t="s">
-        <v>1792</v>
+        <v>1774</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1687</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你成功关闭了阵营模式。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14">
       <c r="C25" t="s">
-        <v>1793</v>
+        <v>1772</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1687</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="关闭阵营模式失败。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14">
       <c r="C26" t="s">
-        <v>1774</v>
+        <v>1775</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1736</v>
       </c>
       <c r="E26" t="s">
         <v>1687</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14">
       <c r="C27" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="D27" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="E27" t="s">
         <v>1687</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14">
       <c r="C28" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D28" t="s">
-        <v>1736</v>
+        <v>1779</v>
       </c>
       <c r="E28" t="s">
         <v>1687</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14">
       <c r="C29" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1777</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1687</v>
+        <v>1792</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14">
       <c r="C30" t="s">
-        <v>1778</v>
+        <v>1793</v>
       </c>
       <c r="D30" t="s">
-        <v>1779</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1687</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
+        <v>1794</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",[20]={},},</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14">
       <c r="C31" t="s">
-        <v>1794</v>
+        <v>1770</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1771</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={},},</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14">
       <c r="C32" t="s">
-        <v>1795</v>
+        <v>1768</v>
       </c>
       <c r="D32" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
+        <v>1769</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={},},</v>
       </c>
     </row>
     <row r="33" spans="1:35">
       <c r="C33" t="s">
-        <v>1770</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1771</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
+        <v>1795</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="34" spans="1:35">
       <c r="C34" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1769</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
+        <v>1796</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
       </c>
     </row>
     <row r="35" spans="1:35">
       <c r="C35" t="s">
-        <v>1797</v>
+        <v>1781</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1730</v>
       </c>
       <c r="N35" t="str">
         <f t="shared" ref="N35:N66" si="1">IF(ISBLANK(B35)=FALSE,IF(ISBLANK(B34),"},["&amp;B35&amp;"]={","["&amp;B35&amp;"]={"),IF(AND(ISBLANK(B35),ISBLANK(C35),ISBLANK(F35),ISBLANK(G35),OR(ISBLANK(B34)=FALSE,ISBLANK(C34)=FALSE,ISBLANK(F34)=FALSE,ISBLANK(G34)=FALSE)),"},},}",IF(ISBLANK(C35),"","{szContent="""&amp;C35&amp;""","&amp;IF(D35&lt;&gt;"","szNote="""&amp;D35&amp;""",","")&amp;IF(E35&lt;&gt;"","col={"&amp;E35&amp;"},","")&amp;IF(F35&gt;0,"bSearch=true,","")&amp;IF(G35&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H35&gt;0,"szVoice="""&amp;H35&amp;""",","")&amp;IF(I35&gt;0,"bTeamChannel=true,","")&amp;IF(J35&gt;0,"bWhisperChannel=true,","")&amp;IF(K35&gt;0,"bCenterAlarm=true,","")&amp;IF(L35&gt;0,"bScreenHead=true,","")&amp;IF(M35&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O35&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O35:AAA35)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你的武斗值增加了20点。\n",[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="36" spans="1:35">
       <c r="C36" t="s">
-        <v>1798</v>
+        <v>1780</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1730</v>
       </c>
       <c r="N36" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你的武斗值增加了30点。\n",[20]={},},</v>
+        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="37" spans="1:35">
       <c r="C37" t="s">
-        <v>1783</v>
+        <v>1797</v>
       </c>
       <c r="E37" t="s">
         <v>1730</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
       <c r="N37" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="C38" t="s">
         <v>1782</v>
       </c>
+      <c r="D38" t="s">
+        <v>1783</v>
+      </c>
       <c r="E38" t="s">
         <v>1730</v>
       </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
       <c r="N38" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]：(%d+)/(1?%d%d)\n",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^密探来报：\"(.-)\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="C39" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D39" t="s">
         <v>1799</v>
       </c>
       <c r="E39" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
+        <v>730</v>
       </c>
       <c r="N39" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^本日还能从本事件获得(%d-)贡献度的奖励。",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},[20]={},},</v>
       </c>
     </row>
     <row r="40" spans="1:35">
       <c r="C40" t="s">
-        <v>1784</v>
+        <v>1800</v>
       </c>
       <c r="D40" t="s">
-        <v>1785</v>
+        <v>1801</v>
       </c>
       <c r="E40" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
+        <v>730</v>
       </c>
       <c r="N40" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35">
-      <c r="C41" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E41" t="s">
-        <v>730</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
+        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},[20]={},},</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:35">
+      <c r="A41" t="s">
+        <v>677</v>
+      </c>
+      <c r="B41">
+        <v>-3</v>
       </c>
       <c r="N41" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)已经添加(.-)为(.-)，将在(%d-)秒后对(.-)开启(.-)战斗。",szNote="{$1}·添加·{$2}·{$3}",col={255,50,50,},bReg=true,[20]={bCenterAlarm=true,},},</v>
-      </c>
-    </row>
-    <row r="42" spans="1:35">
+        <v>},[-3]={</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:35">
       <c r="C42" t="s">
         <v>1802</v>
       </c>
       <c r="D42" t="s">
         <v>1803</v>
       </c>
-      <c r="E42" t="s">
-        <v>730</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
       <c r="N42" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="(.-)对你使用了截元丹，你的原地复活时间被延长了。",szNote="截元丹·【{$1}】",col={255,50,50,},bReg=true,[20]={},},</v>
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",[20]={},},</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:35">
-      <c r="A43" t="s">
-        <v>677</v>
-      </c>
-      <c r="B43">
-        <v>-3</v>
+      <c r="C43" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1805</v>
       </c>
       <c r="N43" t="str">
         <f t="shared" si="1"/>
-        <v>},[-3]={</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:35">
-      <c r="C44" t="s">
-        <v>1804</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1805</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
+        <v>{szContent="侠士",szNote="屏蔽·的卢·诛恶·攻防·刷马",[20]={},},</v>
+      </c>
+    </row>
+    <row r="44" spans="1:35">
+      <c r="A44" t="s">
+        <v>688</v>
+      </c>
+      <c r="B44">
+        <v>-2</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",bSearch=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:35">
+        <v>},[-2]={</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35">
       <c r="C45" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1807</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
+        <v>1784</v>
       </c>
       <c r="N45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="侠士",szNote="屏蔽·的卢·诛恶·攻防·刷马",bSearch=true,[20]={},},</v>
+        <v>{szContent="你已进入地图",[20]={},},</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="46" spans="1:35">
-      <c r="A46" t="s">
-        <v>688</v>
-      </c>
-      <c r="B46">
-        <v>-2</v>
+      <c r="C46" t="s">
+        <v>1816</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1730</v>
       </c>
       <c r="N46" t="str">
         <f t="shared" si="1"/>
-        <v>},[-2]={</v>
+        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="47" spans="1:35">
       <c r="C47" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
+        <v>1782</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1730</v>
       </c>
       <c r="N47" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AB47" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>1813</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>1814</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AH47" t="s">
-        <v>1816</v>
-      </c>
-      <c r="AI47" t="s">
-        <v>1817</v>
+        <v>{szContent="^密探来报：\"(.-)\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},[20]={},},</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="C48" t="s">
-        <v>1818</v>
+        <v>1781</v>
       </c>
       <c r="E48" t="s">
         <v>1730</v>
       </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
       <c r="N48" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^%[(.-)%]服务器：%[(.-)%]大侠，率领%[([浩气盟恶人谷]-)%]阵营侠士们，成功夺得【(.-)】",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},[20]={},},</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>1817</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1818</v>
       </c>
     </row>
     <row r="49" spans="3:29">
       <c r="C49" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1785</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
+        <v>1792</v>
       </c>
       <c r="N49" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^密探来报：%\"(.-)%\"(.-)出现在(.-)[前尘影事]-[“]-([峥嵘振武]-)[”]-([主分线]-)，",szNote="世界首领·出现",col={255,255,100,},bReg=true,[20]={},},</v>
+        <v>{szContent="对方不在线。\n",[20]={},},</v>
       </c>
     </row>
     <row r="50" spans="3:29">
       <c r="C50" t="s">
-        <v>1783</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
+        <v>1793</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1794</v>
       </c>
       <c r="N50" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^你驯养的(.-)[触发]-事件“(.-)”([消除了]-)。",col={255,255,100,},bReg=true,[20]={},},</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>1819</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>1820</v>
+        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",[20]={},},</v>
       </c>
     </row>
     <row r="51" spans="3:29">
       <c r="C51" t="s">
-        <v>1794</v>
+        <v>1819</v>
       </c>
       <c r="N51" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="对方不在线。\n",[20]={},},</v>
+        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
       </c>
     </row>
     <row r="52" spans="3:29">
       <c r="C52" t="s">
-        <v>1795</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
+        <v>1767</v>
       </c>
       <c r="N52" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="已切换到“摁键发言”模式，",szNote="麦克风·摁键发言",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>1820</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>1821</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>1823</v>
       </c>
     </row>
     <row r="53" spans="3:29">
       <c r="C53" t="s">
-        <v>1821</v>
+        <v>1766</v>
       </c>
       <c r="N53" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你无法携带更多的任务奖励道具\n",[20]={},},</v>
+        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
       </c>
     </row>
     <row r="54" spans="3:29">
       <c r="C54" t="s">
-        <v>1767</v>
+        <v>1774</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1687</v>
       </c>
       <c r="N54" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您离开了战场的等待队列。\n",[20]={},},</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>1822</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>1823</v>
-      </c>
-      <c r="AB54" t="s">
-        <v>1824</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>1825</v>
+        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="55" spans="3:29">
       <c r="C55" t="s">
-        <v>1766</v>
+        <v>1772</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1687</v>
       </c>
       <c r="N55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您已经加入战场等待队列。\n",[20]={},},</v>
+        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="56" spans="3:29">
       <c r="C56" t="s">
-        <v>1774</v>
+        <v>1775</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1736</v>
       </c>
       <c r="E56" t="s">
         <v>1687</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="帮会领地唱晚池突现异常，各类鱼儿异常活跃，鱼儿上钩时间大大缩短！各路已满80级的侠士可前往一试，定能收获不菲。\n",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:29">
       <c r="C57" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="D57" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="E57" t="s">
         <v>1687</v>
       </c>
       <c r="N57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="南宫麒：随着暮色降临，扬州、五毒、明教、苍云、战乱天策魂虚场景中的魂灵变得活跃起来，各位方士不妨出魂一探究竟，说不定有意外收获！\n",szNote="方士活动·已经开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:29">
       <c r="C58" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D58" t="s">
-        <v>1736</v>
+        <v>1779</v>
       </c>
       <c r="E58" t="s">
         <v>1687</v>
       </c>
       <c r="N58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山商路运输物资成功开启！请帮会有权限的侠士到黑戈壁帮会物资主簿处申请成为运货首领开始运送！\n",szNote="阴山商路·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={},},</v>
       </c>
     </row>
     <row r="59" spans="3:29">
       <c r="C59" t="s">
-        <v>1776</v>
+        <v>1770</v>
       </c>
       <c r="D59" t="s">
-        <v>1777</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1687</v>
+        <v>1771</v>
       </c>
       <c r="N59" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖急报：巴陵县出现罕见异兽，请深通驭兽秘术之侠客前往收服，以解百姓之忧。\n",szNote="巴陵御兽·开启",col={100,255,255,},[20]={},},</v>
+        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={},},</v>
       </c>
     </row>
     <row r="60" spans="3:29">
       <c r="C60" t="s">
-        <v>1778</v>
+        <v>1768</v>
       </c>
       <c r="D60" t="s">
-        <v>1779</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1687</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
+        <v>1769</v>
       </c>
       <c r="N60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="江湖快报！卫栖梧正在寻找绝世轻功之人，其友[唐文羽]已在少林举办梅花桩试炼大赛，望广大轻功能人速来少林参赛！\n",szNote="扶摇九天·开启",col={100,255,255,},[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={},},</v>
       </c>
     </row>
     <row r="61" spans="3:29">
       <c r="C61" t="s">
-        <v>1770</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1771</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
+        <v>1824</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="援助关系绑定成功，退队可主动解除，但会受到一定惩罚。若对方离线，主动退队解除关系将不受惩罚。\n",szNote="援助·已绑定",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已接受了[大战！",[20]={},},</v>
       </c>
     </row>
     <row r="62" spans="3:29">
       <c r="C62" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D62" t="s">
-        <v>1769</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
+        <v>1825</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="您的宠物已消除忧虑，变得活泼欢快。\n",szNote="宠物已消除忧虑",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="63" spans="3:29">
       <c r="C63" t="s">
-        <v>1781</v>
+        <v>1826</v>
       </c>
       <c r="N63" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖九寨沟·镜海7200平【万年金券】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="64" spans="3:29">
       <c r="C64" t="s">
-        <v>1780</v>
+        <v>1827</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="交易行私货正在拍卖广陵邑7200平【园宅置业·天苑】，侠士们切勿错过！\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="C65" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F65">
-        <v>1</v>
+        <v>1828</v>
       </c>
       <c r="N65" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[大战！",bSearch=true,[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="C66" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="N66" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="你已接受了[江湖秘闻]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="C67" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="N67" t="str">
         <f t="shared" ref="N67:N98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(F67),ISBLANK(G67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(F66)=FALSE,ISBLANK(G66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(E67&lt;&gt;"","col={"&amp;E67&amp;"},","")&amp;IF(F67&gt;0,"bSearch=true,","")&amp;IF(G67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H67&gt;0,"szVoice="""&amp;H67&amp;""",","")&amp;IF(I67&gt;0,"bTeamChannel=true,","")&amp;IF(J67&gt;0,"bWhisperChannel=true,","")&amp;IF(K67&gt;0,"bCenterAlarm=true,","")&amp;IF(L67&gt;0,"bScreenHead=true,","")&amp;IF(M67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O67:AAA67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="你已接受了[潜行狙击]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="C68" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="N68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·顾渚紫笋]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="C69" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="N69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·仙崖石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="C70" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="N70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·峨眉白芽]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="C71" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="N71" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·蒙顶石花]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="C72" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="N72" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[品茶鉴水·西山白露]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="C73" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="N73" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·庐山云雾茶]。\n",[20]={},},</v>
+        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="C74" t="s">
-        <v>1835</v>
+      <c r="A74" t="s">
+        <v>696</v>
+      </c>
+      <c r="B74">
+        <v>-1</v>
       </c>
       <c r="N74" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·仙人掌茶]。\n",[20]={},},</v>
+        <v>},[-1]={</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="C75" t="s">
-        <v>1836</v>
+        <v>1837</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1838</v>
       </c>
       <c r="N75" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·阳羡茶]。\n",[20]={},},</v>
+        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",[20]={},},</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="C76" t="s">
-        <v>1837</v>
+        <v>1839</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1840</v>
       </c>
       <c r="N76" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·霍山黄芽]。\n",[20]={},},</v>
+        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",[20]={},},</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="C77" t="s">
-        <v>1838</v>
+        <v>1841</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1842</v>
       </c>
       <c r="N77" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已接受了[公平交易·方山露芽]。\n",[20]={},},</v>
+        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={},},</v>
       </c>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" t="s">
-        <v>696</v>
-      </c>
-      <c r="B78">
-        <v>-1</v>
+      <c r="C78" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1844</v>
       </c>
       <c r="N78" t="str">
         <f t="shared" si="2"/>
-        <v>},[-1]={</v>
+        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={},},</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="C79" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="D79" t="s">
-        <v>1840</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="K79">
-        <v>1</v>
+        <v>1846</v>
       </c>
       <c r="N79" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已开启自动连放，再次按下可取消\n",szNote="自动连放·已经开启",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={},},</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="C80" t="s">
-        <v>1841</v>
+        <v>1847</v>
       </c>
       <c r="D80" t="s">
-        <v>1842</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="K80">
-        <v>1</v>
+        <v>1848</v>
       </c>
       <c r="N80" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="小队的 {$team} 率先攻击了",szNote="【{$receiver}】开怪了！",bSearch=true,[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={},},</v>
       </c>
     </row>
     <row r="81" spans="3:34">
       <c r="C81" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1844</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
+        <v>1784</v>
       </c>
       <c r="N81" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：自由拾取。\n",szNote="分配模式：自由拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="你已进入地图",[20]={},},</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AG81" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="82" spans="3:34">
       <c r="C82" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="D82" t="s">
-        <v>1846</v>
-      </c>
-      <c r="K82">
-        <v>1</v>
+        <v>1850</v>
       </c>
       <c r="N82" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：队伍拾取。\n",szNote="分配模式：队伍拾取",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={},},</v>
       </c>
     </row>
     <row r="83" spans="3:34">
       <c r="C83" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="D83" t="s">
-        <v>1848</v>
-      </c>
-      <c r="K83">
-        <v>1</v>
+        <v>1852</v>
       </c>
       <c r="N83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：拍团分配。\n",szNote="分配模式：拍团分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={},},</v>
       </c>
     </row>
     <row r="84" spans="3:34">
       <c r="C84" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="D84" t="s">
-        <v>1850</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
+        <v>1854</v>
       </c>
       <c r="N84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="目前队伍分配模式为：分配者分配。\n",szNote="分配模式：分配者分配",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
       </c>
     </row>
     <row r="85" spans="3:34">
       <c r="C85" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
+        <v>1855</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1856</v>
       </c>
       <c r="N85" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="你已进入地图",bSearch=true,[20]={},},</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AA85" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AB85" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AC85" t="s">
-        <v>1812</v>
-      </c>
-      <c r="AD85" t="s">
-        <v>1813</v>
-      </c>
-      <c r="AE85" t="s">
-        <v>1814</v>
-      </c>
-      <c r="AF85" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AG85" t="s">
-        <v>1816</v>
-      </c>
-      <c r="AH85" t="s">
-        <v>1817</v>
+        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={},},</v>
       </c>
     </row>
     <row r="86" spans="3:34">
       <c r="C86" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
       <c r="D86" t="s">
-        <v>1852</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
+        <v>1858</v>
       </c>
       <c r="N86" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已关闭麦克风\n",szNote="麦克风·已关闭",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={},},</v>
       </c>
     </row>
     <row r="87" spans="3:34">
       <c r="C87" t="s">
-        <v>1853</v>
+        <v>1859</v>
       </c>
       <c r="D87" t="s">
-        <v>1854</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
+        <v>1860</v>
       </c>
       <c r="N87" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已切换到“自由发言”模式\n",szNote="麦克风·自由发言",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={},},</v>
       </c>
     </row>
     <row r="88" spans="3:34">
       <c r="C88" t="s">
-        <v>1855</v>
+        <v>1861</v>
       </c>
       <c r="D88" t="s">
-        <v>1856</v>
+        <v>1862</v>
       </c>
       <c r="N88" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您离开了名剑大会的等待队列。\n",szNote="离开排队·名剑大会",[20]={},},</v>
+        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={},},</v>
       </c>
     </row>
     <row r="89" spans="3:34">
       <c r="C89" t="s">
-        <v>1857</v>
+        <v>1863</v>
       </c>
       <c r="D89" t="s">
-        <v>1858</v>
-      </c>
-      <c r="K89">
-        <v>1</v>
+        <v>1864</v>
       </c>
       <c r="N89" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入2对2的名剑大会等待队列中。\n",szNote="排队·名剑大会·2v2",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={},},</v>
       </c>
     </row>
     <row r="90" spans="3:34">
       <c r="C90" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1860</v>
-      </c>
-      <c r="K90">
-        <v>1</v>
+        <v>1865</v>
       </c>
       <c r="N90" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入3对3的名剑大会等待队列中。\n",szNote="排队·名剑大会·3v3",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="91" spans="3:34">
       <c r="C91" t="s">
-        <v>1861</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1862</v>
-      </c>
-      <c r="K91">
-        <v>1</v>
+        <v>1866</v>
       </c>
       <c r="N91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="您已经加入5对5的名剑大会等待队列中。\n",szNote="排队·名剑大会·5v5",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
       </c>
     </row>
     <row r="92" spans="3:34">
       <c r="C92" t="s">
-        <v>1863</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1864</v>
-      </c>
-      <c r="K92">
-        <v>1</v>
+        <v>1867</v>
       </c>
       <c r="N92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="该时间段不能参加名剑大会！\n",szNote="名剑大会·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
       </c>
     </row>
     <row r="93" spans="3:34">
       <c r="C93" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D93" t="s">
-        <v>1866</v>
-      </c>
-      <c r="K93">
-        <v>1</v>
+        <v>1868</v>
       </c>
       <c r="N93" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="当前时间不能进入战场。\n",szNote="战场·非开启时段",[20]={bCenterAlarm=true,},},</v>
+        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
       </c>
     </row>
     <row r="94" spans="3:34">
       <c r="C94" t="s">
-        <v>1867</v>
+        <v>1869</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1870</v>
       </c>
       <c r="N94" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽所有玩家\n",[20]={},},</v>
+        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={},},</v>
       </c>
     </row>
     <row r="95" spans="3:34">
       <c r="C95" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已显示所有玩家\n",[20]={},},</v>
+        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
       </c>
     </row>
     <row r="96" spans="3:34">
       <c r="C96" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="N96" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="已屏蔽其他玩家，仅显示队友\n",[20]={},},</v>
+        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
       </c>
     </row>
     <row r="97" spans="3:14">
       <c r="C97" t="s">
-        <v>1870</v>
-      </c>
+        <v>1802</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E97" t="s">
+        <v>718</v>
+      </c>
+      <c r="F97"/>
       <c r="N97" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="请注意用语和谐，有序发言，切勿发表违规话题。\n",[20]={},},</v>
+        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},[20]={},},</v>
       </c>
     </row>
     <row r="98" spans="3:14">
-      <c r="C98" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D98" t="s">
-        <v>1872</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
       <c r="N98" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="重置自身秘境成功。\n",szNote="重置自身秘境成功",[20]={bTeamChannel=true,},},</v>
-      </c>
-    </row>
-    <row r="99" spans="3:14">
-      <c r="C99" t="s">
-        <v>1873</v>
-      </c>
-      <c r="N99" t="str">
-        <f>IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(F99),ISBLANK(G99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(F98)=FALSE,ISBLANK(G98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(E99&lt;&gt;"","col={"&amp;E99&amp;"},","")&amp;IF(F99&gt;0,"bSearch=true,","")&amp;IF(G99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H99&gt;0,"szVoice="""&amp;H99&amp;""",","")&amp;IF(I99&gt;0,"bTeamChannel=true,","")&amp;IF(J99&gt;0,"bWhisperChannel=true,","")&amp;IF(K99&gt;0,"bCenterAlarm=true,","")&amp;IF(L99&gt;0,"bScreenHead=true,","")&amp;IF(M99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O99:AAA99)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="本日已不能从本事件获得奖励。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="100" spans="3:14">
-      <c r="C100" t="s">
-        <v>1874</v>
-      </c>
-      <c r="N100" t="str">
-        <f>IF(ISBLANK(B100)=FALSE,IF(ISBLANK(B99),"},["&amp;B100&amp;"]={","["&amp;B100&amp;"]={"),IF(AND(ISBLANK(B100),ISBLANK(C100),ISBLANK(F100),ISBLANK(G100),OR(ISBLANK(B99)=FALSE,ISBLANK(C99)=FALSE,ISBLANK(F99)=FALSE,ISBLANK(G99)=FALSE)),"},},}",IF(ISBLANK(C100),"","{szContent="""&amp;C100&amp;""","&amp;IF(D100&lt;&gt;"","szNote="""&amp;D100&amp;""",","")&amp;IF(E100&lt;&gt;"","col={"&amp;E100&amp;"},","")&amp;IF(F100&gt;0,"bSearch=true,","")&amp;IF(G100&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H100&gt;0,"szVoice="""&amp;H100&amp;""",","")&amp;IF(I100&gt;0,"bTeamChannel=true,","")&amp;IF(J100&gt;0,"bWhisperChannel=true,","")&amp;IF(K100&gt;0,"bCenterAlarm=true,","")&amp;IF(L100&gt;0,"bScreenHead=true,","")&amp;IF(M100&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O100&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O100:AAA100)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="本周已不能从本事件获得奖励。\n",[20]={},},</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14">
-      <c r="C101" t="s">
-        <v>1804</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E101" t="s">
-        <v>718</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
-      <c r="N101" t="str">
-        <f>IF(ISBLANK(B101)=FALSE,IF(ISBLANK(B100),"},["&amp;B101&amp;"]={","["&amp;B101&amp;"]={"),IF(AND(ISBLANK(B101),ISBLANK(C101),ISBLANK(F101),ISBLANK(G101),OR(ISBLANK(B100)=FALSE,ISBLANK(C100)=FALSE,ISBLANK(F100)=FALSE,ISBLANK(G100)=FALSE)),"},},}",IF(ISBLANK(C101),"","{szContent="""&amp;C101&amp;""","&amp;IF(D101&lt;&gt;"","szNote="""&amp;D101&amp;""",","")&amp;IF(E101&lt;&gt;"","col={"&amp;E101&amp;"},","")&amp;IF(F101&gt;0,"bSearch=true,","")&amp;IF(G101&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H101&gt;0,"szVoice="""&amp;H101&amp;""",","")&amp;IF(I101&gt;0,"bTeamChannel=true,","")&amp;IF(J101&gt;0,"bWhisperChannel=true,","")&amp;IF(K101&gt;0,"bCenterAlarm=true,","")&amp;IF(L101&gt;0,"bScreenHead=true,","")&amp;IF(M101&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O101&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O101:AAA101)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="财神降临！慷慨之士 {$team} 正在",szNote="【{$receiver}】·正在发红包",col={255,50,255,},bSearch=true,[20]={},},</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14">
-      <c r="N102" t="str">
-        <f>IF(ISBLANK(B102)=FALSE,IF(ISBLANK(B101),"},["&amp;B102&amp;"]={","["&amp;B102&amp;"]={"),IF(AND(ISBLANK(B102),ISBLANK(C102),ISBLANK(F102),ISBLANK(G102),OR(ISBLANK(B101)=FALSE,ISBLANK(C101)=FALSE,ISBLANK(F101)=FALSE,ISBLANK(G101)=FALSE)),"},},}",IF(ISBLANK(C102),"","{szContent="""&amp;C102&amp;""","&amp;IF(D102&lt;&gt;"","szNote="""&amp;D102&amp;""",","")&amp;IF(E102&lt;&gt;"","col={"&amp;E102&amp;"},","")&amp;IF(F102&gt;0,"bSearch=true,","")&amp;IF(G102&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H102&gt;0,"szVoice="""&amp;H102&amp;""",","")&amp;IF(I102&gt;0,"bTeamChannel=true,","")&amp;IF(J102&gt;0,"bWhisperChannel=true,","")&amp;IF(K102&gt;0,"bCenterAlarm=true,","")&amp;IF(L102&gt;0,"bScreenHead=true,","")&amp;IF(M102&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O102&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O102:AAA102)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>
